--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_40_R4.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_40_R4.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>C. EDWARDS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3246</v>
+        <v>4.112</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7578</v>
+        <v>2.6372</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5668</v>
+        <v>1.4748</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3142</v>
+        <v>1.6987</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8187</v>
+        <v>4.0947</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4956</v>
+        <v>-2.396</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1075</v>
+        <v>1.5732</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5581</v>
+        <v>2.4402</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5495</v>
+        <v>-0.867</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7933</v>
+        <v>0.1255</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2606</v>
+        <v>1.6545</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0539</v>
+        <v>-1.529</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4639</v>
+        <v>-3.0154</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5465</v>
+        <v>0.9621</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1142</v>
+        <v>0.3266</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4323</v>
+        <v>0.6355</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>3.0748</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.7527</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. EDWARDS</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1767</v>
+        <v>3.6352</v>
       </c>
       <c r="E3" t="n">
-        <v>1.265</v>
+        <v>3.0684</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9117</v>
+        <v>0.5668</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6987</v>
+        <v>2.3142</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0947</v>
+        <v>0.8187</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.396</v>
+        <v>1.4956</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5732</v>
+        <v>3.1075</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4402</v>
+        <v>0.5581</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.867</v>
+        <v>2.5495</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1255</v>
+        <v>-0.7933</v>
       </c>
       <c r="N3" t="n">
-        <v>1.6545</v>
+        <v>0.2606</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.529</v>
+        <v>-1.0539</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0154</v>
+        <v>-0.4639</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0268</v>
+        <v>0.8571</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0455</v>
+        <v>0.4248</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0723</v>
+        <v>0.4323</v>
       </c>
       <c r="V3" t="n">
-        <v>3.0748</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7527</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>A. PAJOLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0121</v>
+        <v>2.3408</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3718</v>
+        <v>0.9051</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3597</v>
+        <v>1.4357</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6373</v>
+        <v>2.658</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0851</v>
+        <v>2.0156</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5522</v>
+        <v>0.6424</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0475</v>
+        <v>2.3002</v>
       </c>
       <c r="K4" t="n">
-        <v>1.385</v>
+        <v>0.3396</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6625</v>
+        <v>1.9606</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5898</v>
+        <v>0.3579</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7000999999999999</v>
+        <v>1.6761</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1103</v>
+        <v>-1.3182</v>
       </c>
       <c r="P4" t="n">
+        <v>-0.4639</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-1.3917</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-2.7834</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8387</v>
+        <v>0.0048</v>
       </c>
       <c r="T4" t="n">
-        <v>3.0355</v>
+        <v>-0.1452</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1968</v>
+        <v>0.15</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0015</v>
+        <v>2.2944</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0816</v>
+        <v>1.6098</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.6846</v>
       </c>
       <c r="G5" t="n">
         <v>1.1871</v>
@@ -844,13 +844,13 @@
         <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1365</v>
+        <v>0.4294</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4129</v>
+        <v>-0.0589</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7235</v>
+        <v>0.4883</v>
       </c>
       <c r="V5" t="n">
         <v>0.6778999999999999</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PAJOLA</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2724</v>
+        <v>1.7716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0047</v>
+        <v>1.7952</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2677</v>
+        <v>-0.0236</v>
       </c>
       <c r="G6" t="n">
-        <v>2.658</v>
+        <v>2.6373</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0156</v>
+        <v>2.0851</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6424</v>
+        <v>0.5522</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3002</v>
+        <v>2.0475</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3396</v>
+        <v>1.385</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9606</v>
+        <v>0.6625</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3579</v>
+        <v>0.5898</v>
       </c>
       <c r="N6" t="n">
-        <v>1.6761</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3182</v>
+        <v>-0.1103</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>-2.7834</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0635</v>
+        <v>1.5982</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0455</v>
+        <v>1.4589</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.018</v>
+        <v>0.1393</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.614</v>
+        <v>0.9246</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7421</v>
+        <v>-0.4315</v>
       </c>
       <c r="F7" t="n">
         <v>1.356</v>
@@ -1000,10 +1000,10 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3971</v>
+        <v>0.7077</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1098</v>
+        <v>0.2008</v>
       </c>
       <c r="U7" t="n">
         <v>0.507</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>D. HACKETT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5799</v>
+        <v>-0.0052</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-2.1928</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5041</v>
+        <v>2.1876</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5052</v>
+        <v>-1.0264</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1573</v>
+        <v>-1.0264</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6625</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0736</v>
+        <v>-1.4697</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-1.7373</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0736</v>
+        <v>0.2676</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5788</v>
+        <v>0.4433</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1573</v>
+        <v>0.7109</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7361</v>
+        <v>-0.2676</v>
       </c>
       <c r="P8" t="n">
         <v>0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="R8" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3066</v>
+        <v>0.7892</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>-0.0272</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1573</v>
+        <v>0.8164</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. HACKETT</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9302</v>
+        <v>-0.5799</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2858</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3556</v>
+        <v>-0.5041</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0264</v>
+        <v>-0.5052</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0264</v>
+        <v>0.1573</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.6625</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4697</v>
+        <v>0.0736</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7373</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2676</v>
+        <v>0.0736</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4433</v>
+        <v>-0.5788</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7109</v>
+        <v>0.1573</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2676</v>
+        <v>-0.7361</v>
       </c>
       <c r="P9" t="n">
         <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1357</v>
+        <v>-0.3066</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1202</v>
+        <v>-0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9845</v>
+        <v>-0.1573</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7205</v>
+        <v>-1.9674</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3198</v>
+        <v>-0.4312</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0403</v>
+        <v>-1.5362</v>
       </c>
       <c r="G10" t="n">
         <v>0.4862</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.5258</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3882</v>
+        <v>0.6372</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6155</v>
+        <v>-0.1114</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3558</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3023</v>
+        <v>-2.0499</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9061</v>
+        <v>-2.7881</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6038</v>
+        <v>0.7382</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0828</v>
@@ -1312,13 +1312,13 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2917</v>
+        <v>-0.0393</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0677</v>
+        <v>0.0668</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3051</v>
+        <v>-2.55</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8113</v>
+        <v>-2.8546</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5062</v>
+        <v>0.3046</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2424</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7054</v>
+        <v>1.4605</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8259</v>
+        <v>0.7826</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.6778</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1444</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7743</v>
+        <v>-3.3902</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3274</v>
+        <v>-3.8425</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5531</v>
+        <v>0.4523</v>
       </c>
       <c r="G13" t="n">
         <v>-4.6611</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>0.959</v>
+        <v>0.3431</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7512</v>
+        <v>0.2361</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2078</v>
+        <v>0.107</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.789000000000001</v>
+        <v>4.536000000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.3478</v>
+        <v>-2.600799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>7.136699999999998</v>
+        <v>7.136699999999999</v>
       </c>
       <c r="G14" t="n">
         <v>2.520700000000001</v>
@@ -1522,13 +1522,13 @@
         <v>2.179</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7642000000000002</v>
+        <v>-0.7642000000000011</v>
       </c>
       <c r="L14" t="n">
         <v>2.9431</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3418000000000002</v>
+        <v>0.3418000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>8.789400000000001</v>
@@ -1546,19 +1546,19 @@
         <v>10.438</v>
       </c>
       <c r="S14" t="n">
-        <v>6.5852</v>
+        <v>7.332</v>
       </c>
       <c r="T14" t="n">
-        <v>2.833499999999999</v>
+        <v>3.5802</v>
       </c>
       <c r="U14" t="n">
-        <v>3.7516</v>
+        <v>3.7517</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6778999999999997</v>
       </c>
       <c r="W14" t="n">
-        <v>6.716799999999999</v>
+        <v>6.716800000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-7.3947</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9735</v>
+        <v>3.1485</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0254</v>
+        <v>1.4357</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9481</v>
+        <v>1.7129</v>
       </c>
       <c r="G15" t="n">
         <v>2.757</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0154</v>
+        <v>-0.8404</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4604</v>
+        <v>-0.1294</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4758</v>
+        <v>-0.711</v>
       </c>
       <c r="V15" t="n">
         <v>0.5361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3964</v>
+        <v>2.8751</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1498</v>
+        <v>3.0319</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2465</v>
+        <v>-0.1567</v>
       </c>
       <c r="G16" t="n">
         <v>1.9235</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4033</v>
+        <v>-0.118</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.326</v>
+        <v>-0.4439</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7292</v>
+        <v>0.326</v>
       </c>
       <c r="V16" t="n">
         <v>0.1418</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0609</v>
+        <v>2.3196</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7568</v>
+        <v>0.0491</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3042</v>
+        <v>2.2705</v>
       </c>
       <c r="G17" t="n">
         <v>1.0007</v>
@@ -1780,13 +1780,13 @@
         <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0602</v>
+        <v>-0.6811</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6765</v>
+        <v>-0.0312</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6163</v>
+        <v>-0.6499</v>
       </c>
       <c r="V17" t="n">
         <v>1.0722</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. STRAZEL</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7668</v>
+        <v>1.4607</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.783</v>
+        <v>0.0794</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5498</v>
+        <v>1.3813</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2146</v>
+        <v>-3.7682</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5689</v>
+        <v>-5.6855</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7835</v>
+        <v>1.9172</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.418</v>
+        <v>-2.7066</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4719</v>
+        <v>-4.5801</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0539</v>
+        <v>1.8735</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6325</v>
+        <v>-1.0616</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.097</v>
+        <v>-1.1053</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7296</v>
+        <v>0.0437</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>3.0154</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>3.0154</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.52</v>
+        <v>-1.5391</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8136</v>
+        <v>-0.9667</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7064</v>
+        <v>-0.5724</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6083</v>
+        <v>3.7527</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6083</v>
+        <v>3.7527</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>M. STRAZEL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4334</v>
+        <v>1.4238</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7463</v>
+        <v>-0.1932</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1797</v>
+        <v>1.617</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.7682</v>
+        <v>0.2146</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.6855</v>
+        <v>-1.5689</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9172</v>
+        <v>1.7835</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.7066</v>
+        <v>-0.418</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.5801</v>
+        <v>-1.4719</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8735</v>
+        <v>1.0539</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0616</v>
+        <v>0.6325</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1053</v>
+        <v>-0.097</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0437</v>
+        <v>0.7296</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0154</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>3.0154</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.5664</v>
+        <v>-0.863</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.7924</v>
+        <v>-0.2238</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.774</v>
+        <v>-0.6392</v>
       </c>
       <c r="V19" t="n">
-        <v>3.7527</v>
+        <v>1.6083</v>
       </c>
       <c r="W19" t="n">
-        <v>3.7527</v>
+        <v>1.6083</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.224</v>
+        <v>-0.3486</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7074</v>
+        <v>0.2356</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4834</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4047</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6286</v>
+        <v>0.056</v>
       </c>
       <c r="T20" t="n">
-        <v>0.637</v>
+        <v>0.1652</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0083</v>
+        <v>-0.1092</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5096</v>
+        <v>-1.5345</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3963</v>
+        <v>-1.5656</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8867</v>
+        <v>0.0311</v>
       </c>
       <c r="G21" t="n">
-        <v>1.244</v>
+        <v>-0.7541</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2904</v>
+        <v>1.287</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9535</v>
+        <v>-2.0411</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5583</v>
+        <v>-1.0941</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2416</v>
+        <v>0.0504</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7999</v>
+        <v>-1.1445</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3143</v>
+        <v>0.34</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5321</v>
+        <v>1.2366</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8464</v>
+        <v>-0.8966</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8979</v>
+        <v>-0.7804</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4753</v>
+        <v>-0.4716</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4226</v>
+        <v>-0.3088</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9885</v>
+        <v>-1.8127</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6836</v>
+        <v>-2.6322</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3049</v>
+        <v>0.8195</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7541</v>
+        <v>1.244</v>
       </c>
       <c r="H22" t="n">
-        <v>1.287</v>
+        <v>0.2904</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0411</v>
+        <v>0.9535</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0941</v>
+        <v>1.5583</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0504</v>
+        <v>-0.2416</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1445</v>
+        <v>1.7999</v>
       </c>
       <c r="M22" t="n">
-        <v>0.34</v>
+        <v>-0.3143</v>
       </c>
       <c r="N22" t="n">
-        <v>1.2366</v>
+        <v>0.5321</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8966</v>
+        <v>-0.8464</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2344</v>
+        <v>-1.201</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5895</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6449</v>
+        <v>-0.4898</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.9034</v>
+        <v>-5.4151</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3723</v>
+        <v>-2.0184</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5311</v>
+        <v>-3.3967</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3204</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8303</v>
+        <v>-0.342</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8962</v>
+        <v>-0.5423</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0659</v>
+        <v>0.2003</v>
       </c>
       <c r="V23" t="n">
         <v>-3.7527</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2426</v>
+        <v>-5.9059</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7946</v>
+        <v>-5.5587</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.448</v>
+        <v>-0.3472</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4132</v>
@@ -2326,13 +2326,13 @@
         <v>2.7834</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6128</v>
+        <v>-0.2761</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.3967</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0198</v>
+        <v>0.1206</v>
       </c>
       <c r="V24" t="n">
         <v>-2.6805</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.789100000000001</v>
+        <v>-3.789099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.1367</v>
+        <v>-7.1364</v>
       </c>
       <c r="F25" t="n">
-        <v>3.347600000000001</v>
+        <v>3.3475</v>
       </c>
       <c r="G25" t="n">
         <v>-2.520799999999999</v>
@@ -2407,16 +2407,16 @@
         <v>-6.585100000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.7517</v>
+        <v>-3.7516</v>
       </c>
       <c r="U25" t="n">
         <v>-2.8334</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6779000000000006</v>
+        <v>0.6778999999999997</v>
       </c>
       <c r="W25" t="n">
-        <v>7.3947</v>
+        <v>7.394699999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-6.716799999999999</v>
